--- a/examples/sequence/OUL/metadata.xlsx
+++ b/examples/sequence/OUL/metadata.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="21">
   <si>
     <t xml:space="preserve">Animal</t>
   </si>
@@ -40,7 +40,10 @@
     <t xml:space="preserve">Center</t>
   </si>
   <si>
-    <t xml:space="preserve">Meter_Pixel_Ratio</t>
+    <t xml:space="preserve">MetersPerPixel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all</t>
   </si>
   <si>
     <t xml:space="preserve">control</t>
@@ -89,7 +92,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -111,6 +114,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -155,7 +164,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -166,6 +175,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -186,7 +199,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultColWidth="10.46875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.4609375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="21.81"/>
   </cols>
@@ -217,11 +230,21 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="F2" s="1" t="n">
         <v>0</v>
       </c>
@@ -231,7 +254,9 @@
       <c r="H2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I2" s="1"/>
+      <c r="I2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -241,25 +266,25 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -270,25 +295,25 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -299,25 +324,25 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -328,25 +353,25 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -357,25 +382,25 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -386,25 +411,25 @@
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -415,25 +440,25 @@
         <v>3</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -444,25 +469,25 @@
         <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -473,25 +498,25 @@
         <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -502,25 +527,25 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -531,25 +556,25 @@
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -560,25 +585,25 @@
         <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -589,25 +614,25 @@
         <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="I15" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -618,25 +643,25 @@
         <v>5</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="I16" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -647,25 +672,25 @@
         <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="I17" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -676,25 +701,25 @@
         <v>6</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="I18" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/examples/sequence/OUL/metadata.xlsx
+++ b/examples/sequence/OUL/metadata.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="21">
   <si>
     <t xml:space="preserve">Animal</t>
   </si>
@@ -46,22 +46,43 @@
     <t xml:space="preserve">all</t>
   </si>
   <si>
-    <t xml:space="preserve">controll</t>
+    <t xml:space="preserve">control</t>
   </si>
   <si>
     <t xml:space="preserve">m</t>
   </si>
   <si>
-    <t xml:space="preserve">2_304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coh_7_8</t>
+    <t xml:space="preserve">1_160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coh_1_2</t>
   </si>
   <si>
     <t xml:space="preserve">tg</t>
   </si>
   <si>
-    <t xml:space="preserve">control</t>
+    <t xml:space="preserve">f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2_116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coh_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1_136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coh_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2_206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1_211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coh_5_6</t>
   </si>
 </sst>
 </file>
@@ -71,7 +92,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -93,6 +114,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -137,7 +164,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -148,6 +175,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -167,10 +198,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1048576"/>
-  <sheetFormatPr defaultColWidth="10.4765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr defaultColWidth="10.4609375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="23.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="21.81"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -198,20 +229,20 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="1" t="n">
@@ -223,16 +254,16 @@
       <c r="H2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>304</v>
+        <v>160</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
@@ -241,7 +272,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
@@ -258,10 +289,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>305</v>
+        <v>161</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
@@ -270,7 +301,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>10</v>
@@ -287,16 +318,16 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
-        <v>381</v>
+        <v>162</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>4</v>
@@ -316,16 +347,16 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>382</v>
+        <v>163</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>4</v>
@@ -345,39 +376,39 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>383</v>
+        <v>116</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
-        <v>384</v>
+        <v>117</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>12</v>
@@ -386,37 +417,371 @@
         <v>9</v>
       </c>
       <c r="E8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B13" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="0" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="C13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="F1:H1"/>

--- a/examples/sequence/OUL/metadata.xlsx
+++ b/examples/sequence/OUL/metadata.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="animal" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="24">
   <si>
     <t xml:space="preserve">Animal</t>
   </si>
@@ -65,6 +65,12 @@
     <t xml:space="preserve">coh_5_6</t>
   </si>
   <si>
+    <t xml:space="preserve">coh_9_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coh_7_8</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sequence</t>
   </si>
   <si>
@@ -84,6 +90,9 @@
   </si>
   <si>
     <t xml:space="preserve">1_211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2_304</t>
   </si>
 </sst>
 </file>
@@ -201,11 +210,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="10.15234375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultColWidth="10.171875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.49"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="1" width="10.16"/>
   </cols>
   <sheetData>
@@ -584,8 +593,232 @@
       <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>378</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>379</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>385</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>387</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>388</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="0"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
+        <v>305</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="0"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>381</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>382</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
+        <v>383</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
+        <v>384</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -603,8 +836,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
-  <sheetFormatPr defaultColWidth="10.4140625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:N1048576"/>
+  <sheetFormatPr defaultColWidth="10.43359375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="10.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="16.35"/>
@@ -616,10 +849,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -636,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -651,7 +884,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -666,7 +899,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -683,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -698,7 +931,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -713,7 +946,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -730,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -745,7 +978,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -760,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -777,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -792,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -807,7 +1040,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -824,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -839,7 +1072,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -854,7 +1087,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -871,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -886,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -901,7 +1134,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -915,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -927,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -939,7 +1172,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -953,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -965,7 +1198,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -977,7 +1210,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -991,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -1003,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -1015,7 +1248,7 @@
         <v>2</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -1029,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -1041,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -1053,7 +1286,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -1067,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -1079,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -1091,7 +1324,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -1105,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -1117,7 +1350,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -1129,7 +1362,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -1143,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -1155,7 +1388,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -1167,7 +1400,7 @@
         <v>2</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -1181,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -1193,7 +1426,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -1205,7 +1438,7 @@
         <v>2</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -1219,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -1231,7 +1464,7 @@
         <v>1</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -1243,7 +1476,7 @@
         <v>2</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -1257,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -1269,7 +1502,7 @@
         <v>1</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -1281,14 +1514,335 @@
         <v>2</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
     </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="n">
+        <v>378</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3"/>
+      <c r="B51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3"/>
+      <c r="B52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="n">
+        <v>379</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3"/>
+      <c r="B54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3"/>
+      <c r="B55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="n">
+        <v>385</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3"/>
+      <c r="B57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3"/>
+      <c r="B58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="n">
+        <v>387</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3"/>
+      <c r="B60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3"/>
+      <c r="B61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="n">
+        <v>388</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3"/>
+      <c r="B63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3"/>
+      <c r="B64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3"/>
+      <c r="B66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3"/>
+      <c r="B67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3" t="n">
+        <v>305</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3"/>
+      <c r="B69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3"/>
+      <c r="B70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="n">
+        <v>381</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3"/>
+      <c r="B72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3"/>
+      <c r="B73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="3" t="n">
+        <v>382</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="3"/>
+      <c r="B75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3"/>
+      <c r="B76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3" t="n">
+        <v>383</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="3"/>
+      <c r="B78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3"/>
+      <c r="B79" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3" t="n">
+        <v>384</v>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="3"/>
+      <c r="B81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="3"/>
+      <c r="B82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="28">
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
@@ -1306,6 +1860,17 @@
     <mergeCell ref="A41:A43"/>
     <mergeCell ref="A44:A46"/>
     <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A80:A82"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>

--- a/examples/sequence/OUL/metadata.xlsx
+++ b/examples/sequence/OUL/metadata.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="animal" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="23">
   <si>
     <t xml:space="preserve">Animal</t>
   </si>
@@ -59,6 +59,12 @@
     <t xml:space="preserve">coh_7_8</t>
   </si>
   <si>
+    <t xml:space="preserve">coh_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coh_12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sequence</t>
   </si>
   <si>
@@ -66,6 +72,24 @@
   </si>
   <si>
     <t xml:space="preserve">2_304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">529_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">528_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">527_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">533_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">534_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">535_2</t>
   </si>
 </sst>
 </file>
@@ -183,11 +207,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1048576"/>
-  <sheetFormatPr defaultColWidth="10.171875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultColWidth="10.15234375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.5"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="1" width="10.16"/>
   </cols>
   <sheetData>
@@ -316,22 +340,22 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="2" t="n">
         <v>304</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="B7" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G7" s="4"/>
@@ -339,22 +363,22 @@
       <c r="I7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="2" t="n">
         <v>305</v>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="B8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G8" s="4"/>
@@ -368,16 +392,16 @@
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="4" t="n">
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -388,16 +412,16 @@
       <c r="B10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="4" t="n">
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -408,16 +432,16 @@
       <c r="B11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="4" t="n">
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -428,35 +452,239 @@
       <c r="B12" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="4" t="n">
+      <c r="C12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="n">
+        <v>527</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="n">
+        <v>530</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="n">
+        <v>531</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="n">
+        <v>532</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="n">
+        <v>533</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="n">
+        <v>534</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="n">
+        <v>535</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="n">
+        <v>546</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="n">
+        <v>547</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -473,8 +701,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N1048576"/>
-  <sheetFormatPr defaultColWidth="10.4453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:N67"/>
+  <sheetFormatPr defaultColWidth="10.4375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="10.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="16.35"/>
@@ -486,10 +714,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -650,8 +878,8 @@
       <c r="B17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>14</v>
+      <c r="C17" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -659,8 +887,8 @@
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>14</v>
+      <c r="C18" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -668,8 +896,8 @@
       <c r="B19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>14</v>
+      <c r="C19" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -679,8 +907,8 @@
       <c r="B20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>14</v>
+      <c r="C20" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -688,8 +916,8 @@
       <c r="B21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>14</v>
+      <c r="C21" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -697,8 +925,8 @@
       <c r="B22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>14</v>
+      <c r="C22" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -708,8 +936,8 @@
       <c r="B23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>14</v>
+      <c r="C23" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -717,8 +945,8 @@
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>14</v>
+      <c r="C24" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -726,8 +954,8 @@
       <c r="B25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>14</v>
+      <c r="C25" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -737,8 +965,8 @@
       <c r="B26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>14</v>
+      <c r="C26" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -746,8 +974,8 @@
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>14</v>
+      <c r="C27" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -755,8 +983,8 @@
       <c r="B28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>14</v>
+      <c r="C28" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -766,8 +994,8 @@
       <c r="B29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>14</v>
+      <c r="C29" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -775,8 +1003,8 @@
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>14</v>
+      <c r="C30" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -784,8 +1012,8 @@
       <c r="B31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>14</v>
+      <c r="C31" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -795,8 +1023,8 @@
       <c r="B32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>14</v>
+      <c r="C32" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -804,8 +1032,8 @@
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>14</v>
+      <c r="C33" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -813,62 +1041,331 @@
       <c r="B34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="C34" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="n">
+        <v>527</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3"/>
+      <c r="B36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3"/>
+      <c r="B37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="n">
+        <v>528</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3"/>
+      <c r="B39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3"/>
+      <c r="B40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="n">
+        <v>529</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3"/>
+      <c r="B42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3"/>
+      <c r="B43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="n">
+        <v>530</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3"/>
+      <c r="B45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3"/>
+      <c r="B46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="n">
+        <v>531</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3"/>
+      <c r="B48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3"/>
+      <c r="B49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="n">
+        <v>532</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3"/>
+      <c r="B51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3"/>
+      <c r="B52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="n">
+        <v>533</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3"/>
+      <c r="B54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3"/>
+      <c r="B55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="n">
+        <v>534</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3"/>
+      <c r="B57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3"/>
+      <c r="B58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="n">
+        <v>535</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3"/>
+      <c r="B60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3"/>
+      <c r="B61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="n">
+        <v>546</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3"/>
+      <c r="B63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3"/>
+      <c r="B64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3" t="n">
+        <v>547</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3"/>
+      <c r="B66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3"/>
+      <c r="B67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="23">
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
@@ -881,6 +1378,17 @@
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
